--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10917" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10917" uniqueCount="560">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource Bundle du flux d'alimentation des mesures de biologie à envoyer au serveur</t>
+    <t>Profil biologie de la ressource Bundle du flux d'alimentation des mesures de biologie à transmettre</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>Bundle.entry</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>Entry in the bundle - will have a resource or information</t>
@@ -3928,7 +3925,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>176</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -3946,10 +3943,10 @@
         <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3988,16 +3985,16 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AC17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AC17" t="s" s="2">
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>175</v>
@@ -4012,7 +4009,7 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -4029,10 +4026,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4141,10 +4138,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4255,10 +4252,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4371,10 +4368,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4400,10 +4397,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4454,7 +4451,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4483,10 +4480,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4512,13 +4509,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4568,7 +4565,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4597,10 +4594,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4623,13 +4620,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4680,7 +4677,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4709,10 +4706,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4738,10 +4735,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4792,7 +4789,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4801,7 +4798,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4821,10 +4818,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4933,10 +4930,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5047,10 +5044,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5163,10 +5160,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5192,13 +5189,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5227,11 +5224,11 @@
         <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5277,10 +5274,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5303,16 +5300,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5362,7 +5359,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5391,10 +5388,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5420,10 +5417,10 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5474,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5483,7 +5480,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5503,10 +5500,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5615,10 +5612,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5729,10 +5726,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5845,10 +5842,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5874,10 +5871,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5907,11 +5904,11 @@
         <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5928,7 +5925,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5957,10 +5954,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5986,13 +5983,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6042,7 +6039,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -6071,10 +6068,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6100,10 +6097,10 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6154,7 +6151,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6183,10 +6180,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6212,10 +6209,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6266,7 +6263,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6295,10 +6292,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6324,10 +6321,10 @@
         <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6378,7 +6375,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6407,10 +6404,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6436,10 +6433,10 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6490,7 +6487,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6519,10 +6516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6548,10 +6545,10 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6602,7 +6599,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6611,7 +6608,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6631,10 +6628,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6743,10 +6740,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6857,10 +6854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6973,10 +6970,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7002,10 +6999,10 @@
         <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7056,7 +7053,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7085,10 +7082,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7114,10 +7111,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7168,7 +7165,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7197,10 +7194,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7226,13 +7223,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7282,7 +7279,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7311,10 +7308,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7340,13 +7337,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7396,7 +7393,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7425,10 +7422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7451,16 +7448,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7510,7 +7507,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7539,20 +7536,20 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>87</v>
@@ -7570,10 +7567,10 @@
         <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7636,7 +7633,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7653,10 +7650,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7765,10 +7762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7879,10 +7876,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7995,10 +7992,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8024,10 +8021,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8078,7 +8075,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8107,10 +8104,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8136,13 +8133,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8192,7 +8189,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8221,14 +8218,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8247,16 +8244,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8306,7 +8303,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8321,10 +8318,10 @@
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8335,10 +8332,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8364,10 +8361,10 @@
         <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8418,7 +8415,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8427,7 +8424,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8447,10 +8444,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8559,10 +8556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8673,10 +8670,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8789,10 +8786,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8818,13 +8815,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8853,11 +8850,11 @@
         <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8874,7 +8871,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8903,10 +8900,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8929,16 +8926,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8988,7 +8985,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9017,10 +9014,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9046,10 +9043,10 @@
         <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9100,7 +9097,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9109,7 +9106,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -9129,10 +9126,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9241,10 +9238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9355,10 +9352,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9471,10 +9468,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9500,10 +9497,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9515,7 +9512,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9533,11 +9530,11 @@
         <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9554,7 +9551,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -9583,10 +9580,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9612,13 +9609,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9629,7 +9626,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9668,7 +9665,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9697,10 +9694,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9726,10 +9723,10 @@
         <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9780,7 +9777,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9809,10 +9806,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9838,10 +9835,10 @@
         <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9892,7 +9889,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9921,10 +9918,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9950,10 +9947,10 @@
         <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10004,7 +10001,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10033,10 +10030,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10062,10 +10059,10 @@
         <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10116,7 +10113,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10145,10 +10142,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10174,10 +10171,10 @@
         <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10228,7 +10225,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10237,7 +10234,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -10257,10 +10254,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10369,10 +10366,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10483,10 +10480,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10599,10 +10596,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10628,10 +10625,10 @@
         <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10682,7 +10679,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10711,10 +10708,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10740,10 +10737,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10794,7 +10791,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10823,10 +10820,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10852,13 +10849,13 @@
         <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10908,7 +10905,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10937,10 +10934,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10966,13 +10963,13 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11022,7 +11019,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11051,10 +11048,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11077,16 +11074,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11136,7 +11133,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11165,20 +11162,20 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>87</v>
@@ -11196,10 +11193,10 @@
         <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11262,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -11279,10 +11276,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11391,10 +11388,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11505,10 +11502,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11621,10 +11618,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11650,10 +11647,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11704,7 +11701,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11733,10 +11730,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11762,13 +11759,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11818,7 +11815,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11847,14 +11844,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11873,16 +11870,16 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11932,7 +11929,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11947,10 +11944,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11961,10 +11958,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11990,10 +11987,10 @@
         <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12044,7 +12041,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12053,7 +12050,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -12073,10 +12070,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12185,10 +12182,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12299,10 +12296,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12415,10 +12412,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12444,13 +12441,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12479,11 +12476,11 @@
         <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
       </c>
@@ -12500,7 +12497,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12529,10 +12526,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12555,16 +12552,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12614,7 +12611,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12643,10 +12640,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12672,10 +12669,10 @@
         <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12726,7 +12723,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12735,7 +12732,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12755,10 +12752,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12867,10 +12864,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12981,10 +12978,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13097,10 +13094,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13126,10 +13123,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13141,7 +13138,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13159,11 +13156,11 @@
         <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
       </c>
@@ -13180,7 +13177,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -13209,10 +13206,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13238,13 +13235,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13255,7 +13252,7 @@
         <v>77</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>77</v>
@@ -13294,7 +13291,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -13323,10 +13320,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13352,10 +13349,10 @@
         <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13406,7 +13403,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13435,10 +13432,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13464,10 +13461,10 @@
         <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13518,7 +13515,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13547,10 +13544,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13576,10 +13573,10 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13630,7 +13627,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13659,10 +13656,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13688,10 +13685,10 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13742,7 +13739,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13771,10 +13768,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13800,10 +13797,10 @@
         <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13854,7 +13851,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13863,7 +13860,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13883,10 +13880,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13995,10 +13992,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14109,10 +14106,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14225,10 +14222,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14254,10 +14251,10 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14308,7 +14305,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -14337,10 +14334,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14366,10 +14363,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14420,7 +14417,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14449,10 +14446,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14478,13 +14475,13 @@
         <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14534,7 +14531,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14563,10 +14560,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14592,13 +14589,13 @@
         <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14648,7 +14645,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14677,10 +14674,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14703,16 +14700,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14762,7 +14759,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14791,20 +14788,20 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>87</v>
@@ -14822,10 +14819,10 @@
         <v>145</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14888,7 +14885,7 @@
         <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
@@ -14905,10 +14902,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15017,10 +15014,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15131,10 +15128,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15247,10 +15244,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15276,10 +15273,10 @@
         <v>80</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15330,7 +15327,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15359,10 +15356,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15388,13 +15385,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15444,7 +15441,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15473,14 +15470,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15499,16 +15496,16 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15558,7 +15555,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15573,10 +15570,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL119" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15587,10 +15584,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15616,10 +15613,10 @@
         <v>145</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15670,7 +15667,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15679,7 +15676,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15699,10 +15696,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15811,10 +15808,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15925,10 +15922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16041,10 +16038,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16070,13 +16067,13 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16105,11 +16102,11 @@
         <v>127</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z124" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA124" t="s" s="2">
         <v>77</v>
       </c>
@@ -16126,7 +16123,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16155,10 +16152,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16181,16 +16178,16 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16240,7 +16237,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16269,10 +16266,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16298,10 +16295,10 @@
         <v>145</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16352,7 +16349,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16361,7 +16358,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -16381,10 +16378,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16493,10 +16490,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16607,10 +16604,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16723,10 +16720,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16752,10 +16749,10 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16767,7 +16764,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16785,11 +16782,11 @@
         <v>127</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z130" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>77</v>
       </c>
@@ -16806,7 +16803,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16835,10 +16832,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16864,13 +16861,13 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16881,7 +16878,7 @@
         <v>77</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>77</v>
@@ -16920,7 +16917,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>87</v>
@@ -16949,10 +16946,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16978,10 +16975,10 @@
         <v>150</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17032,7 +17029,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17061,10 +17058,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17090,10 +17087,10 @@
         <v>132</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17144,7 +17141,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17173,10 +17170,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17202,10 +17199,10 @@
         <v>150</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17256,7 +17253,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17285,10 +17282,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17314,10 +17311,10 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17368,7 +17365,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17397,10 +17394,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17426,10 +17423,10 @@
         <v>145</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17480,7 +17477,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17489,7 +17486,7 @@
         <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>99</v>
@@ -17509,10 +17506,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17621,10 +17618,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17735,10 +17732,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17851,10 +17848,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17880,10 +17877,10 @@
         <v>150</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17934,7 +17931,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17963,10 +17960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17992,10 +17989,10 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18046,7 +18043,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18075,10 +18072,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18104,13 +18101,13 @@
         <v>150</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18160,7 +18157,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18189,10 +18186,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18218,13 +18215,13 @@
         <v>132</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18274,7 +18271,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18303,10 +18300,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18329,16 +18326,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18388,7 +18385,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18417,20 +18414,20 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>87</v>
@@ -18448,10 +18445,10 @@
         <v>145</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18514,7 +18511,7 @@
         <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>77</v>
@@ -18531,10 +18528,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18643,10 +18640,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18757,10 +18754,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18873,10 +18870,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18902,10 +18899,10 @@
         <v>80</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -18956,7 +18953,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -18985,10 +18982,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19014,13 +19011,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19070,7 +19067,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19099,14 +19096,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19125,16 +19122,16 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19184,7 +19181,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19199,10 +19196,10 @@
         <v>77</v>
       </c>
       <c r="AK151" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL151" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -19213,10 +19210,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19242,10 +19239,10 @@
         <v>145</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19296,7 +19293,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19305,7 +19302,7 @@
         <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>99</v>
@@ -19325,10 +19322,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19437,10 +19434,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19551,10 +19548,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19667,10 +19664,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19696,13 +19693,13 @@
         <v>107</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19731,11 +19728,11 @@
         <v>127</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>77</v>
       </c>
@@ -19752,7 +19749,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -19781,10 +19778,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19807,16 +19804,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19866,7 +19863,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -19895,10 +19892,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19924,10 +19921,10 @@
         <v>145</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -19978,7 +19975,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -19987,7 +19984,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -20007,10 +20004,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20119,10 +20116,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20233,10 +20230,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20349,10 +20346,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20378,10 +20375,10 @@
         <v>107</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20393,7 +20390,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -20411,11 +20408,11 @@
         <v>127</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z162" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA162" t="s" s="2">
         <v>77</v>
       </c>
@@ -20432,7 +20429,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20461,10 +20458,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20490,13 +20487,13 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -20507,7 +20504,7 @@
         <v>77</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>77</v>
@@ -20546,7 +20543,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>87</v>
@@ -20575,10 +20572,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20604,10 +20601,10 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -20658,7 +20655,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20687,10 +20684,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20716,10 +20713,10 @@
         <v>132</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20770,7 +20767,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -20799,10 +20796,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20828,10 +20825,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20882,7 +20879,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -20911,10 +20908,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20940,10 +20937,10 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20994,7 +20991,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21023,10 +21020,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21052,10 +21049,10 @@
         <v>145</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21106,7 +21103,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21115,7 +21112,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>99</v>
@@ -21135,10 +21132,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21247,10 +21244,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21361,10 +21358,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21477,10 +21474,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21506,10 +21503,10 @@
         <v>150</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21560,7 +21557,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>87</v>
@@ -21589,10 +21586,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21618,10 +21615,10 @@
         <v>101</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -21672,7 +21669,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -21701,10 +21698,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21730,13 +21727,13 @@
         <v>150</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -21786,7 +21783,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -21815,10 +21812,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21844,13 +21841,13 @@
         <v>132</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21900,7 +21897,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -21929,10 +21926,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21955,16 +21952,16 @@
         <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -22014,7 +22011,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -22043,13 +22040,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>77</v>
@@ -22074,10 +22071,10 @@
         <v>145</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -22140,7 +22137,7 @@
         <v>77</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>77</v>
@@ -22157,10 +22154,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22269,10 +22266,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22383,10 +22380,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22499,10 +22496,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22528,10 +22525,10 @@
         <v>80</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -22582,7 +22579,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -22611,10 +22608,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22640,13 +22637,13 @@
         <v>101</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -22696,7 +22693,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -22725,14 +22722,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22751,16 +22748,16 @@
         <v>77</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="N183" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -22810,7 +22807,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -22825,10 +22822,10 @@
         <v>77</v>
       </c>
       <c r="AK183" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL183" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
@@ -22839,10 +22836,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22868,10 +22865,10 @@
         <v>145</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -22922,7 +22919,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -22931,7 +22928,7 @@
         <v>87</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>99</v>
@@ -22951,10 +22948,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23063,10 +23060,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23177,10 +23174,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23293,10 +23290,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23322,13 +23319,13 @@
         <v>107</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -23357,11 +23354,11 @@
         <v>127</v>
       </c>
       <c r="Y188" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z188" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z188" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
       </c>
@@ -23378,7 +23375,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -23407,10 +23404,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23433,16 +23430,16 @@
         <v>88</v>
       </c>
       <c r="K189" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L189" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L189" t="s" s="2">
+      <c r="M189" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M189" t="s" s="2">
+      <c r="N189" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -23492,7 +23489,7 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
@@ -23521,10 +23518,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23550,10 +23547,10 @@
         <v>145</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M190" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -23604,7 +23601,7 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
@@ -23613,7 +23610,7 @@
         <v>87</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>99</v>
@@ -23633,10 +23630,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23745,10 +23742,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23859,10 +23856,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23975,10 +23972,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24004,10 +24001,10 @@
         <v>107</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -24019,7 +24016,7 @@
         <v>77</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>77</v>
@@ -24037,11 +24034,11 @@
         <v>127</v>
       </c>
       <c r="Y194" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z194" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z194" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA194" t="s" s="2">
         <v>77</v>
       </c>
@@ -24058,7 +24055,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>87</v>
@@ -24087,10 +24084,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24116,13 +24113,13 @@
         <v>101</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -24133,7 +24130,7 @@
         <v>77</v>
       </c>
       <c r="S195" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T195" t="s" s="2">
         <v>77</v>
@@ -24172,7 +24169,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>87</v>
@@ -24201,10 +24198,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24230,10 +24227,10 @@
         <v>150</v>
       </c>
       <c r="L196" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24284,7 +24281,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -24313,10 +24310,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24342,10 +24339,10 @@
         <v>132</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -24396,7 +24393,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -24425,10 +24422,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24454,10 +24451,10 @@
         <v>150</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -24508,7 +24505,7 @@
         <v>77</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>78</v>
@@ -24537,10 +24534,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24566,10 +24563,10 @@
         <v>150</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M199" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -24620,7 +24617,7 @@
         <v>77</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>78</v>
@@ -24649,10 +24646,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24678,10 +24675,10 @@
         <v>145</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -24732,7 +24729,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -24741,7 +24738,7 @@
         <v>87</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>99</v>
@@ -24761,10 +24758,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24873,10 +24870,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24987,10 +24984,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25103,10 +25100,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25132,10 +25129,10 @@
         <v>150</v>
       </c>
       <c r="L204" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M204" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -25186,7 +25183,7 @@
         <v>77</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>87</v>
@@ -25215,10 +25212,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25244,10 +25241,10 @@
         <v>101</v>
       </c>
       <c r="L205" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M205" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -25298,7 +25295,7 @@
         <v>77</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>78</v>
@@ -25327,10 +25324,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25356,13 +25353,13 @@
         <v>150</v>
       </c>
       <c r="L206" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M206" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M206" t="s" s="2">
+      <c r="N206" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -25412,7 +25409,7 @@
         <v>77</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>78</v>
@@ -25441,10 +25438,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25470,13 +25467,13 @@
         <v>132</v>
       </c>
       <c r="L207" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M207" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M207" t="s" s="2">
+      <c r="N207" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -25526,7 +25523,7 @@
         <v>77</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>78</v>
@@ -25555,10 +25552,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25581,16 +25578,16 @@
         <v>88</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M208" t="s" s="2">
+      <c r="N208" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -25640,7 +25637,7 @@
         <v>77</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>78</v>
@@ -25669,13 +25666,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>77</v>
@@ -25700,10 +25697,10 @@
         <v>145</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -25766,7 +25763,7 @@
         <v>77</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>77</v>
@@ -25783,10 +25780,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25895,10 +25892,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26009,10 +26006,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26125,10 +26122,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26154,10 +26151,10 @@
         <v>80</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M213" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -26208,7 +26205,7 @@
         <v>77</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>78</v>
@@ -26237,10 +26234,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26266,13 +26263,13 @@
         <v>101</v>
       </c>
       <c r="L214" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M214" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M214" t="s" s="2">
+      <c r="N214" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -26322,7 +26319,7 @@
         <v>77</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>78</v>
@@ -26351,14 +26348,14 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -26377,16 +26374,16 @@
         <v>77</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M215" t="s" s="2">
+      <c r="N215" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -26436,7 +26433,7 @@
         <v>77</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>78</v>
@@ -26451,10 +26448,10 @@
         <v>77</v>
       </c>
       <c r="AK215" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL215" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL215" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>77</v>
@@ -26465,10 +26462,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26494,10 +26491,10 @@
         <v>145</v>
       </c>
       <c r="L216" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M216" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -26548,7 +26545,7 @@
         <v>77</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>78</v>
@@ -26557,7 +26554,7 @@
         <v>87</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>99</v>
@@ -26577,10 +26574,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26689,10 +26686,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26803,10 +26800,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26919,10 +26916,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26948,13 +26945,13 @@
         <v>107</v>
       </c>
       <c r="L220" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M220" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M220" t="s" s="2">
+      <c r="N220" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -26983,11 +26980,11 @@
         <v>127</v>
       </c>
       <c r="Y220" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z220" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z220" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA220" t="s" s="2">
         <v>77</v>
       </c>
@@ -27004,7 +27001,7 @@
         <v>77</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>78</v>
@@ -27033,10 +27030,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -27059,16 +27056,16 @@
         <v>88</v>
       </c>
       <c r="K221" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L221" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L221" t="s" s="2">
+      <c r="M221" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M221" t="s" s="2">
+      <c r="N221" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
@@ -27118,7 +27115,7 @@
         <v>77</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>78</v>
@@ -27147,10 +27144,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27176,10 +27173,10 @@
         <v>145</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -27230,7 +27227,7 @@
         <v>77</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>78</v>
@@ -27239,7 +27236,7 @@
         <v>87</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>99</v>
@@ -27259,10 +27256,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27371,10 +27368,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27485,10 +27482,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27601,10 +27598,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27630,10 +27627,10 @@
         <v>107</v>
       </c>
       <c r="L226" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M226" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -27645,7 +27642,7 @@
         <v>77</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>77</v>
@@ -27663,11 +27660,11 @@
         <v>127</v>
       </c>
       <c r="Y226" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z226" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z226" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA226" t="s" s="2">
         <v>77</v>
       </c>
@@ -27684,7 +27681,7 @@
         <v>77</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>87</v>
@@ -27713,10 +27710,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27742,13 +27739,13 @@
         <v>101</v>
       </c>
       <c r="L227" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M227" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M227" t="s" s="2">
+      <c r="N227" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -27759,7 +27756,7 @@
         <v>77</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T227" t="s" s="2">
         <v>77</v>
@@ -27798,7 +27795,7 @@
         <v>77</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>87</v>
@@ -27827,10 +27824,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27856,10 +27853,10 @@
         <v>150</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -27910,7 +27907,7 @@
         <v>77</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
@@ -27939,10 +27936,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27968,10 +27965,10 @@
         <v>132</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -28022,7 +28019,7 @@
         <v>77</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>78</v>
@@ -28051,10 +28048,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -28080,10 +28077,10 @@
         <v>150</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -28134,7 +28131,7 @@
         <v>77</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>
@@ -28163,10 +28160,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -28192,10 +28189,10 @@
         <v>150</v>
       </c>
       <c r="L231" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M231" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -28246,7 +28243,7 @@
         <v>77</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>78</v>
@@ -28275,10 +28272,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28304,10 +28301,10 @@
         <v>145</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -28358,7 +28355,7 @@
         <v>77</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>78</v>
@@ -28367,7 +28364,7 @@
         <v>87</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>99</v>
@@ -28387,10 +28384,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28499,10 +28496,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28613,10 +28610,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28729,10 +28726,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28758,10 +28755,10 @@
         <v>150</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M236" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -28812,7 +28809,7 @@
         <v>77</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>87</v>
@@ -28841,10 +28838,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28870,10 +28867,10 @@
         <v>101</v>
       </c>
       <c r="L237" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M237" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -28924,7 +28921,7 @@
         <v>77</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>78</v>
@@ -28953,10 +28950,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28982,13 +28979,13 @@
         <v>150</v>
       </c>
       <c r="L238" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M238" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M238" t="s" s="2">
+      <c r="N238" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
@@ -29038,7 +29035,7 @@
         <v>77</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>78</v>
@@ -29067,10 +29064,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -29096,13 +29093,13 @@
         <v>132</v>
       </c>
       <c r="L239" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M239" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M239" t="s" s="2">
+      <c r="N239" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -29152,7 +29149,7 @@
         <v>77</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>78</v>
@@ -29181,10 +29178,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -29207,16 +29204,16 @@
         <v>88</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L240" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M240" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M240" t="s" s="2">
+      <c r="N240" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -29266,7 +29263,7 @@
         <v>77</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>78</v>
@@ -29295,13 +29292,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>77</v>
@@ -29326,10 +29323,10 @@
         <v>145</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -29392,7 +29389,7 @@
         <v>77</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK241" t="s" s="2">
         <v>77</v>
@@ -29409,10 +29406,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -29521,10 +29518,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -29635,10 +29632,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29751,10 +29748,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -29780,10 +29777,10 @@
         <v>80</v>
       </c>
       <c r="L245" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M245" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -29834,7 +29831,7 @@
         <v>77</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>78</v>
@@ -29863,10 +29860,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -29892,13 +29889,13 @@
         <v>101</v>
       </c>
       <c r="L246" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M246" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M246" t="s" s="2">
+      <c r="N246" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -29948,7 +29945,7 @@
         <v>77</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>78</v>
@@ -29977,14 +29974,14 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E247" s="2"/>
       <c r="F247" t="s" s="2">
@@ -30003,16 +30000,16 @@
         <v>77</v>
       </c>
       <c r="K247" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L247" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L247" t="s" s="2">
+      <c r="M247" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M247" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="N247" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
@@ -30062,7 +30059,7 @@
         <v>77</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>78</v>
@@ -30077,10 +30074,10 @@
         <v>77</v>
       </c>
       <c r="AK247" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL247" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM247" t="s" s="2">
         <v>77</v>
@@ -30091,10 +30088,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -30120,10 +30117,10 @@
         <v>145</v>
       </c>
       <c r="L248" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M248" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -30174,7 +30171,7 @@
         <v>77</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>78</v>
@@ -30183,7 +30180,7 @@
         <v>87</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>99</v>
@@ -30203,10 +30200,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -30315,10 +30312,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -30429,10 +30426,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -30545,10 +30542,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -30574,13 +30571,13 @@
         <v>107</v>
       </c>
       <c r="L252" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M252" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M252" t="s" s="2">
+      <c r="N252" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
@@ -30609,11 +30606,11 @@
         <v>127</v>
       </c>
       <c r="Y252" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z252" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z252" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA252" t="s" s="2">
         <v>77</v>
       </c>
@@ -30630,7 +30627,7 @@
         <v>77</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>78</v>
@@ -30659,10 +30656,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -30685,16 +30682,16 @@
         <v>88</v>
       </c>
       <c r="K253" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L253" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L253" t="s" s="2">
+      <c r="M253" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M253" t="s" s="2">
+      <c r="N253" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
@@ -30744,7 +30741,7 @@
         <v>77</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>78</v>
@@ -30773,10 +30770,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -30802,10 +30799,10 @@
         <v>145</v>
       </c>
       <c r="L254" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M254" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -30856,7 +30853,7 @@
         <v>77</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>78</v>
@@ -30865,7 +30862,7 @@
         <v>87</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>99</v>
@@ -30885,10 +30882,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -30997,10 +30994,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -31111,10 +31108,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -31227,10 +31224,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -31256,10 +31253,10 @@
         <v>107</v>
       </c>
       <c r="L258" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M258" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M258" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" s="2"/>
@@ -31271,7 +31268,7 @@
         <v>77</v>
       </c>
       <c r="S258" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T258" t="s" s="2">
         <v>77</v>
@@ -31289,11 +31286,11 @@
         <v>127</v>
       </c>
       <c r="Y258" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z258" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z258" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA258" t="s" s="2">
         <v>77</v>
       </c>
@@ -31310,7 +31307,7 @@
         <v>77</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>87</v>
@@ -31339,10 +31336,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -31368,13 +31365,13 @@
         <v>101</v>
       </c>
       <c r="L259" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M259" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M259" t="s" s="2">
+      <c r="N259" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N259" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
@@ -31385,7 +31382,7 @@
         <v>77</v>
       </c>
       <c r="S259" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T259" t="s" s="2">
         <v>77</v>
@@ -31424,7 +31421,7 @@
         <v>77</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>87</v>
@@ -31453,10 +31450,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -31482,10 +31479,10 @@
         <v>150</v>
       </c>
       <c r="L260" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M260" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M260" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
@@ -31536,7 +31533,7 @@
         <v>77</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>78</v>
@@ -31565,10 +31562,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -31594,10 +31591,10 @@
         <v>132</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N261" s="2"/>
       <c r="O261" s="2"/>
@@ -31648,7 +31645,7 @@
         <v>77</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>78</v>
@@ -31677,10 +31674,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -31706,10 +31703,10 @@
         <v>150</v>
       </c>
       <c r="L262" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M262" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M262" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -31760,7 +31757,7 @@
         <v>77</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>78</v>
@@ -31789,10 +31786,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -31818,10 +31815,10 @@
         <v>150</v>
       </c>
       <c r="L263" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M263" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M263" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -31872,7 +31869,7 @@
         <v>77</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>78</v>
@@ -31901,10 +31898,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -31930,10 +31927,10 @@
         <v>145</v>
       </c>
       <c r="L264" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M264" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M264" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -31984,7 +31981,7 @@
         <v>77</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>78</v>
@@ -31993,7 +31990,7 @@
         <v>87</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>99</v>
@@ -32013,10 +32010,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -32125,10 +32122,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -32239,10 +32236,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -32355,10 +32352,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -32384,10 +32381,10 @@
         <v>150</v>
       </c>
       <c r="L268" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M268" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M268" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" s="2"/>
@@ -32438,7 +32435,7 @@
         <v>77</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>87</v>
@@ -32467,10 +32464,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -32496,10 +32493,10 @@
         <v>101</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -32550,7 +32547,7 @@
         <v>77</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>78</v>
@@ -32579,10 +32576,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -32608,13 +32605,13 @@
         <v>150</v>
       </c>
       <c r="L270" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M270" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M270" t="s" s="2">
+      <c r="N270" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N270" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O270" s="2"/>
       <c r="P270" t="s" s="2">
@@ -32664,7 +32661,7 @@
         <v>77</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>78</v>
@@ -32693,10 +32690,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -32722,13 +32719,13 @@
         <v>132</v>
       </c>
       <c r="L271" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M271" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M271" t="s" s="2">
+      <c r="N271" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N271" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O271" s="2"/>
       <c r="P271" t="s" s="2">
@@ -32778,7 +32775,7 @@
         <v>77</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>78</v>
@@ -32807,10 +32804,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -32833,16 +32830,16 @@
         <v>88</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L272" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M272" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M272" t="s" s="2">
+      <c r="N272" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N272" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
@@ -32892,7 +32889,7 @@
         <v>77</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>78</v>
@@ -32921,13 +32918,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>77</v>
@@ -32952,10 +32949,10 @@
         <v>145</v>
       </c>
       <c r="L273" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M273" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M273" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N273" s="2"/>
       <c r="O273" s="2"/>
@@ -33018,7 +33015,7 @@
         <v>77</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>77</v>
@@ -33035,10 +33032,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -33147,10 +33144,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -33261,10 +33258,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -33377,10 +33374,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -33406,10 +33403,10 @@
         <v>80</v>
       </c>
       <c r="L277" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M277" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M277" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -33460,7 +33457,7 @@
         <v>77</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>78</v>
@@ -33489,10 +33486,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -33518,13 +33515,13 @@
         <v>101</v>
       </c>
       <c r="L278" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M278" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M278" t="s" s="2">
+      <c r="N278" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N278" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O278" s="2"/>
       <c r="P278" t="s" s="2">
@@ -33574,7 +33571,7 @@
         <v>77</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>78</v>
@@ -33603,14 +33600,14 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
@@ -33629,16 +33626,16 @@
         <v>77</v>
       </c>
       <c r="K279" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L279" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L279" t="s" s="2">
+      <c r="M279" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M279" t="s" s="2">
+      <c r="N279" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
@@ -33688,7 +33685,7 @@
         <v>77</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>78</v>
@@ -33703,10 +33700,10 @@
         <v>77</v>
       </c>
       <c r="AK279" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AL279" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AM279" t="s" s="2">
         <v>77</v>
@@ -33717,10 +33714,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -33746,10 +33743,10 @@
         <v>145</v>
       </c>
       <c r="L280" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M280" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M280" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N280" s="2"/>
       <c r="O280" s="2"/>
@@ -33800,7 +33797,7 @@
         <v>77</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>78</v>
@@ -33809,7 +33806,7 @@
         <v>87</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>99</v>
@@ -33829,10 +33826,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -33941,10 +33938,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -34055,10 +34052,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -34171,10 +34168,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -34200,13 +34197,13 @@
         <v>107</v>
       </c>
       <c r="L284" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M284" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M284" t="s" s="2">
+      <c r="N284" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N284" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O284" s="2"/>
       <c r="P284" t="s" s="2">
@@ -34235,11 +34232,11 @@
         <v>127</v>
       </c>
       <c r="Y284" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z284" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z284" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="AA284" t="s" s="2">
         <v>77</v>
       </c>
@@ -34256,7 +34253,7 @@
         <v>77</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>78</v>
@@ -34285,10 +34282,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -34311,16 +34308,16 @@
         <v>88</v>
       </c>
       <c r="K285" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L285" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L285" t="s" s="2">
+      <c r="M285" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M285" t="s" s="2">
+      <c r="N285" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N285" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O285" s="2"/>
       <c r="P285" t="s" s="2">
@@ -34370,7 +34367,7 @@
         <v>77</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>78</v>
@@ -34399,10 +34396,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -34428,10 +34425,10 @@
         <v>145</v>
       </c>
       <c r="L286" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M286" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M286" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" s="2"/>
@@ -34482,7 +34479,7 @@
         <v>77</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>78</v>
@@ -34491,7 +34488,7 @@
         <v>87</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>99</v>
@@ -34511,10 +34508,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -34623,10 +34620,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -34737,10 +34734,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -34853,10 +34850,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -34882,10 +34879,10 @@
         <v>107</v>
       </c>
       <c r="L290" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M290" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M290" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="2"/>
@@ -34897,7 +34894,7 @@
         <v>77</v>
       </c>
       <c r="S290" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T290" t="s" s="2">
         <v>77</v>
@@ -34915,11 +34912,11 @@
         <v>127</v>
       </c>
       <c r="Y290" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z290" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z290" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA290" t="s" s="2">
         <v>77</v>
       </c>
@@ -34936,7 +34933,7 @@
         <v>77</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>87</v>
@@ -34965,10 +34962,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -34994,13 +34991,13 @@
         <v>101</v>
       </c>
       <c r="L291" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M291" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M291" t="s" s="2">
+      <c r="N291" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N291" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
@@ -35011,7 +35008,7 @@
         <v>77</v>
       </c>
       <c r="S291" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T291" t="s" s="2">
         <v>77</v>
@@ -35050,7 +35047,7 @@
         <v>77</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>87</v>
@@ -35079,10 +35076,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -35108,10 +35105,10 @@
         <v>150</v>
       </c>
       <c r="L292" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M292" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M292" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
@@ -35162,7 +35159,7 @@
         <v>77</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>78</v>
@@ -35191,10 +35188,10 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -35220,10 +35217,10 @@
         <v>132</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N293" s="2"/>
       <c r="O293" s="2"/>
@@ -35274,7 +35271,7 @@
         <v>77</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>78</v>
@@ -35303,10 +35300,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -35332,10 +35329,10 @@
         <v>150</v>
       </c>
       <c r="L294" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M294" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M294" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" s="2"/>
@@ -35386,7 +35383,7 @@
         <v>77</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>78</v>
@@ -35415,10 +35412,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -35444,10 +35441,10 @@
         <v>150</v>
       </c>
       <c r="L295" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M295" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M295" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N295" s="2"/>
       <c r="O295" s="2"/>
@@ -35498,7 +35495,7 @@
         <v>77</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>78</v>
@@ -35527,10 +35524,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -35556,10 +35553,10 @@
         <v>145</v>
       </c>
       <c r="L296" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M296" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M296" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N296" s="2"/>
       <c r="O296" s="2"/>
@@ -35610,7 +35607,7 @@
         <v>77</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>78</v>
@@ -35619,7 +35616,7 @@
         <v>87</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>99</v>
@@ -35639,10 +35636,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -35751,10 +35748,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -35865,10 +35862,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -35981,10 +35978,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -36010,10 +36007,10 @@
         <v>150</v>
       </c>
       <c r="L300" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M300" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M300" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N300" s="2"/>
       <c r="O300" s="2"/>
@@ -36064,7 +36061,7 @@
         <v>77</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>87</v>
@@ -36093,10 +36090,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -36122,10 +36119,10 @@
         <v>101</v>
       </c>
       <c r="L301" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M301" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M301" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N301" s="2"/>
       <c r="O301" s="2"/>
@@ -36176,7 +36173,7 @@
         <v>77</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>78</v>
@@ -36205,10 +36202,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -36234,13 +36231,13 @@
         <v>150</v>
       </c>
       <c r="L302" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M302" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M302" t="s" s="2">
+      <c r="N302" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N302" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O302" s="2"/>
       <c r="P302" t="s" s="2">
@@ -36290,7 +36287,7 @@
         <v>77</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>78</v>
@@ -36319,10 +36316,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -36348,13 +36345,13 @@
         <v>132</v>
       </c>
       <c r="L303" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M303" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M303" t="s" s="2">
+      <c r="N303" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N303" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" t="s" s="2">
@@ -36404,7 +36401,7 @@
         <v>77</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>78</v>
@@ -36433,10 +36430,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -36459,16 +36456,16 @@
         <v>88</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L304" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M304" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M304" t="s" s="2">
+      <c r="N304" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N304" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O304" s="2"/>
       <c r="P304" t="s" s="2">
@@ -36518,7 +36515,7 @@
         <v>77</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>78</v>
@@ -36547,10 +36544,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -36573,19 +36570,19 @@
         <v>88</v>
       </c>
       <c r="K305" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L305" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L305" t="s" s="2">
+      <c r="M305" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M305" t="s" s="2">
+      <c r="N305" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N305" t="s" s="2">
+      <c r="O305" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O305" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P305" t="s" s="2">
         <v>77</v>
@@ -36634,7 +36631,7 @@
         <v>77</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>78</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}mesures-inv-1:Si le cholestérol HDL est présent, alors le cholestérol total doit également être présent. {entry.resource.where(code = '2085-9').exists() implies entry.resource.where(code = '2093-3').exists()}mesures-inv-2:Si le cholestérol total est présent, alors le cholestérol hdl doit également être présent. {entry.resource.where(code = '2093-3').exists() implies entry.resource.where(code = '2085-9').exists()}</t>
   </si>
   <si>
     <t>N/A</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}mesures-inv-1:Si le cholestérol HDL est présent, alors le cholestérol total doit également être présent. {entry.resource.where(code = '2085-9').exists() implies entry.resource.where(code = '2093-3').exists()}mesures-inv-2:Si le cholestérol total est présent, alors le cholestérol hdl doit également être présent. {entry.resource.where(code = '2093-3').exists() implies entry.resource.where(code = '2085-9').exists()}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}mesures-inv-1:Si le cholestérol HDL est présent, alors le cholestérol total doit également être présent. {entry.resource.where(code = '2085-9').exists() implies entry.resource.where(code = '2093-3').exists()}mesures-inv-2:Si le cholestérol total est présent, alors le cholestérol HDL doit également être présent. {entry.resource.where(code = '2093-3').exists() implies entry.resource.where(code = '2085-9').exists()}</t>
   </si>
   <si>
     <t>N/A</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation-biologie.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10917" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10916" uniqueCount="559">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1311,10 +1311,6 @@
   </si>
   <si>
     <t>Bundle.entry:mes-observation-ratio.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observation {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-cholesterol-ratio}
-</t>
   </si>
   <si>
     <t>Bundle.entry:mes-observation-ratio.search</t>
@@ -22729,7 +22725,7 @@
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22745,20 +22741,18 @@
         <v>77</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>418</v>
+        <v>193</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>276</v>
+        <v>194</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>77</v>
@@ -22822,10 +22816,10 @@
         <v>77</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
@@ -22836,7 +22830,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>196</v>
@@ -22948,7 +22942,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>200</v>
@@ -23060,7 +23054,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>201</v>
@@ -23174,7 +23168,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>202</v>
@@ -23290,7 +23284,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>203</v>
@@ -23404,7 +23398,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>209</v>
@@ -23518,7 +23512,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>214</v>
@@ -23529,7 +23523,7 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G190" t="s" s="2">
         <v>87</v>
@@ -23630,7 +23624,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>218</v>
@@ -23742,7 +23736,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>219</v>
@@ -23856,7 +23850,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>220</v>
@@ -23972,7 +23966,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>221</v>
@@ -24016,7 +24010,7 @@
         <v>77</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>77</v>
@@ -24084,7 +24078,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>226</v>
@@ -24130,7 +24124,7 @@
         <v>77</v>
       </c>
       <c r="S195" t="s" s="2">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="T195" t="s" s="2">
         <v>77</v>
@@ -24198,7 +24192,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>230</v>
@@ -24310,7 +24304,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>233</v>
@@ -24422,7 +24416,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>235</v>
@@ -24534,7 +24528,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>238</v>
@@ -24646,7 +24640,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>241</v>
@@ -24758,7 +24752,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>245</v>
@@ -24870,7 +24864,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>246</v>
@@ -24984,7 +24978,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>247</v>
@@ -25100,7 +25094,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>248</v>
@@ -25212,7 +25206,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>251</v>
@@ -25324,7 +25318,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>254</v>
@@ -25438,7 +25432,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>258</v>
@@ -25552,7 +25546,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>262</v>
@@ -25666,13 +25660,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>77</v>
@@ -25780,7 +25774,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>182</v>
@@ -25892,7 +25886,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>183</v>
@@ -26006,7 +26000,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>184</v>
@@ -26122,7 +26116,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>185</v>
@@ -26234,7 +26228,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>188</v>
@@ -26348,7 +26342,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>192</v>
@@ -26374,7 +26368,7 @@
         <v>77</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>276</v>
@@ -26462,7 +26456,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>196</v>
@@ -26574,7 +26568,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>200</v>
@@ -26686,7 +26680,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>201</v>
@@ -26800,7 +26794,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>202</v>
@@ -26916,7 +26910,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>203</v>
@@ -27030,7 +27024,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>209</v>
@@ -27144,7 +27138,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>214</v>
@@ -27256,7 +27250,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>218</v>
@@ -27368,7 +27362,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>219</v>
@@ -27482,7 +27476,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>220</v>
@@ -27598,7 +27592,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>221</v>
@@ -27710,7 +27704,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>226</v>
@@ -27824,7 +27818,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>230</v>
@@ -27936,7 +27930,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>233</v>
@@ -28048,7 +28042,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>235</v>
@@ -28160,7 +28154,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>238</v>
@@ -28272,7 +28266,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>241</v>
@@ -28384,7 +28378,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>245</v>
@@ -28496,7 +28490,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>246</v>
@@ -28610,7 +28604,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>247</v>
@@ -28726,7 +28720,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>248</v>
@@ -28838,7 +28832,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>251</v>
@@ -28950,7 +28944,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>254</v>
@@ -29064,7 +29058,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>258</v>
@@ -29178,7 +29172,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>262</v>
@@ -29292,13 +29286,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>77</v>
@@ -29406,7 +29400,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>182</v>
@@ -29518,7 +29512,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>183</v>
@@ -29632,7 +29626,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>184</v>
@@ -29748,7 +29742,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>185</v>
@@ -29860,7 +29854,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>188</v>
@@ -29974,7 +29968,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>192</v>
@@ -30000,13 +29994,13 @@
         <v>77</v>
       </c>
       <c r="K247" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L247" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L247" t="s" s="2">
+      <c r="M247" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N247" t="s" s="2">
         <v>278</v>
@@ -30088,7 +30082,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>196</v>
@@ -30200,7 +30194,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>200</v>
@@ -30312,7 +30306,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>201</v>
@@ -30426,7 +30420,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>202</v>
@@ -30542,7 +30536,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>203</v>
@@ -30656,7 +30650,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>209</v>
@@ -30770,7 +30764,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>214</v>
@@ -30882,7 +30876,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>218</v>
@@ -30994,7 +30988,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>219</v>
@@ -31108,7 +31102,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>220</v>
@@ -31224,7 +31218,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>221</v>
@@ -31336,7 +31330,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>226</v>
@@ -31450,7 +31444,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>230</v>
@@ -31562,7 +31556,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>233</v>
@@ -31674,7 +31668,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>235</v>
@@ -31786,7 +31780,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>238</v>
@@ -31898,7 +31892,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>241</v>
@@ -32010,7 +32004,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>245</v>
@@ -32122,7 +32116,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>246</v>
@@ -32236,7 +32230,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>247</v>
@@ -32352,7 +32346,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>248</v>
@@ -32464,7 +32458,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>251</v>
@@ -32576,7 +32570,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>254</v>
@@ -32690,7 +32684,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>258</v>
@@ -32804,7 +32798,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>262</v>
@@ -32918,13 +32912,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>77</v>
@@ -33032,7 +33026,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>182</v>
@@ -33144,7 +33138,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>183</v>
@@ -33258,7 +33252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>184</v>
@@ -33374,7 +33368,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>185</v>
@@ -33486,7 +33480,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>188</v>
@@ -33600,14 +33594,14 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
@@ -33626,16 +33620,16 @@
         <v>77</v>
       </c>
       <c r="K279" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L279" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L279" t="s" s="2">
+      <c r="M279" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M279" t="s" s="2">
+      <c r="N279" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
@@ -33700,7 +33694,7 @@
         <v>77</v>
       </c>
       <c r="AK279" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AL279" t="s" s="2">
         <v>280</v>
@@ -33714,7 +33708,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>196</v>
@@ -33826,7 +33820,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>200</v>
@@ -33938,7 +33932,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>201</v>
@@ -34052,7 +34046,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>202</v>
@@ -34168,7 +34162,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>203</v>
@@ -34282,7 +34276,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>209</v>
@@ -34396,7 +34390,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>214</v>
@@ -34508,7 +34502,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>218</v>
@@ -34620,7 +34614,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>219</v>
@@ -34734,7 +34728,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>220</v>
@@ -34850,7 +34844,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>221</v>
@@ -34962,7 +34956,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>226</v>
@@ -35008,7 +35002,7 @@
         <v>77</v>
       </c>
       <c r="S291" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T291" t="s" s="2">
         <v>77</v>
@@ -35076,7 +35070,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>230</v>
@@ -35188,7 +35182,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>233</v>
@@ -35300,7 +35294,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>235</v>
@@ -35412,7 +35406,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>238</v>
@@ -35524,7 +35518,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>241</v>
@@ -35636,7 +35630,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>245</v>
@@ -35748,7 +35742,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>246</v>
@@ -35862,7 +35856,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>247</v>
@@ -35978,7 +35972,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>248</v>
@@ -36090,7 +36084,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>251</v>
@@ -36202,7 +36196,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>254</v>
@@ -36316,7 +36310,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>258</v>
@@ -36430,7 +36424,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>262</v>
@@ -36544,10 +36538,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -36570,19 +36564,19 @@
         <v>88</v>
       </c>
       <c r="K305" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L305" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L305" t="s" s="2">
+      <c r="M305" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M305" t="s" s="2">
+      <c r="N305" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N305" t="s" s="2">
+      <c r="O305" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="O305" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P305" t="s" s="2">
         <v>77</v>
@@ -36631,7 +36625,7 @@
         <v>77</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>78</v>
